--- a/.mvn/resource/TestResults.xlsx
+++ b/.mvn/resource/TestResults.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="25">
   <si>
     <t>TestCaseName</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>Sort failed</t>
+  </si>
+  <si>
+    <t>Amazon.com. Spend less. Smile more.</t>
+  </si>
+  <si>
+    <t>Search failed</t>
   </si>
 </sst>
 </file>
@@ -153,11 +159,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
@@ -508,12 +542,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="22.40234375"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="28.8984375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="20.50390625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="31.89453125"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="6.40625"/>
   </cols>
   <sheetData>
@@ -755,6 +789,202 @@
         <v>10</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D18" t="s" s="21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s" s="22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s" s="24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s" s="26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D22" t="s" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="D23" t="s" s="30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s" s="33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s" s="35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D26" t="s" s="36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s" s="38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D28" t="s" s="41">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D29" t="s" s="42">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D30" t="s" s="44">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="D31" t="s" s="46">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
